--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-12-2025.xlsx
@@ -592,23 +592,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -712,23 +712,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -832,23 +832,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -952,23 +952,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -1072,23 +1072,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -1192,23 +1192,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -1312,23 +1312,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -1432,23 +1432,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -1552,23 +1552,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -1672,23 +1672,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -1792,23 +1792,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -1912,23 +1912,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -2032,23 +2032,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -2152,23 +2152,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -2272,23 +2272,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -2609,23 +2609,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -2729,23 +2729,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -2849,23 +2849,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -2969,23 +2969,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
@@ -3449,23 +3449,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7ccf38245
-	0x7ff7ccf382a0
-	0x7ff7ccd1165d
-	0x7ff7ccd69a33
-	0x7ff7ccd69d3c
-	0x7ff7ccdbdf67
-	0x7ff7ccdbac97
-	0x7ff7ccd5ac29
-	0x7ff7ccd5ba93
-	0x7ff7cd24ffe0
-	0x7ff7cd24a920
-	0x7ff7cd269086
-	0x7ff7ccf55744
-	0x7ff7ccf5e6ec
-	0x7ff7ccf41964
-	0x7ff7ccf41b15
-	0x7ff7ccf27842
+	0x7ff63cca8245
+	0x7ff63cca82a0
+	0x7ff63ca8165d
+	0x7ff63cad9a33
+	0x7ff63cad9d3c
+	0x7ff63cb2df67
+	0x7ff63cb2ac97
+	0x7ff63cacac29
+	0x7ff63cacba93
+	0x7ff63cfbffe0
+	0x7ff63cfba920
+	0x7ff63cfd9086
+	0x7ff63ccc5744
+	0x7ff63ccce6ec
+	0x7ff63ccb1964
+	0x7ff63ccb1b15
+	0x7ff63cc97842
 	0x7ffb6b03e8d7
 	0x7ffb6bfac53c
 </t>
